--- a/tests/e2e/default/enketo/forms/select_from_file.xlsx
+++ b/tests/e2e/default/enketo/forms/select_from_file.xlsx
@@ -334,7 +334,7 @@
     <t xml:space="preserve">color</t>
   </si>
   <si>
-    <t xml:space="preserve">Select your favorite color</t>
+    <t xml:space="preserve">Select a color</t>
   </si>
   <si>
     <t xml:space="preserve">form_title</t>
@@ -1273,7 +1273,7 @@
       <formula>AND(C2="",NOT(ISERROR(MATCH(B2,{"end_group","end_repeat"},0))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D1003">
+  <conditionalFormatting sqref="D4:D1003 D2">
     <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>AND(OR(NOT(ISERROR(MATCH(B2,{"acknowledge","audio","date","datetime","decimal","file","geopoint","geoshape","geotrace","image","integer","note","range","rank","text","time","video"},0))),LEFT(B2,11)="select_one ",LEFT(B2,16)="select_multiple ",LEFT(B2,21)="select_one_from_file ",LEFT(B2,26)="select_multiple_from_file "),D2="")</formula>
     </cfRule>
@@ -1284,27 +1284,27 @@
       <formula>OR(D2="NO_LABEL",D2="DELETE_THIS_LINE")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:BC1003">
+  <conditionalFormatting sqref="B2:BC2 B4:BC1003 B3:C3 E3:BC3">
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>AND($B2="begin_group",B$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:BC1003">
+  <conditionalFormatting sqref="B2:BC2 B4:BC1003 B3:C3 E3:BC3">
     <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>AND($B2="end_group",B$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:BC1003">
+  <conditionalFormatting sqref="B2:BC2 B4:BC1003 B3:C3 E3:BC3">
     <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>AND($B2="begin_repeat",B$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:BC1003">
+  <conditionalFormatting sqref="B2:BC2 B4:BC1003 B3:C3 E3:BC3">
     <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>AND($B2="end_repeat",B$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:BC1003">
+  <conditionalFormatting sqref="A2:BC2 A4:BC1003 A3:C3 E3:BC3">
     <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>AND(A2&lt;&gt;"",A$1="")</formula>
     </cfRule>
@@ -1330,6 +1330,42 @@
     </cfRule>
     <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>AND(OR(NOT(ISERROR(MATCH(B3,{"acknowledge","audio","date","datetime","decimal","file","geopoint","geoshape","geotrace","image","integer","note","range","rank","text","time","video"},0))),LEFT(B3,11)="select_one ",LEFT(B3,16)="select_multiple ",LEFT(B3,21)="select_one_from_file ",LEFT(B3,26)="select_multiple_from_file "),D3="")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>AND(D3&lt;&gt;"",NOT(ISERROR(MATCH(B3,{"calculate","end","end_group","end_repeat","hidden","start","today"},0))))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>OR(D3="NO_LABEL",D3="DELETE_THIS_LINE")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>AND($B3="begin_group",D$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>AND($B3="end_group",D$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>AND($B3="begin_repeat",D$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>AND($B3="end_repeat",D$1&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>AND(D3&lt;&gt;"",D$1="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -1387,7 +1423,7 @@
       </c>
       <c r="B2" s="3" t="str">
         <f aca="true">TEXT(NOW(), "yyyymmddhhmmss")</f>
-        <v>20260925111004</v>
+        <v>20260925172008</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>12</v>
